--- a/aec/results/신촌/feature_selection_report.xlsx
+++ b/aec/results/신촌/feature_selection_report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상관계수_전체" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상관계수_Top20" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIF_선택feature" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TAMA_분포_성별" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="상관계수_전체" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="상관계수_Top20" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="VIF_선택feature" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="TAMA_분포_성별" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/aec/results/신촌/feature_selection_report.xlsx
+++ b/aec/results/신촌/feature_selection_report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="상관계수_전체" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="상관계수_Top20" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="VIF_선택feature" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="TAMA_분포_성별" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상관계수_전체" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="상관계수_Top20" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIF_선택feature" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TAMA_분포_성별" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -479,34 +479,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>peak_max_height</t>
+          <t>p25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.2934e-01</t>
+          <t>2.4966e-01</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.2455e-16</t>
+          <t>1.9851e-19</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2.0972e-01</t>
+          <t>2.5726e-01</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>4.2336e-14</t>
+          <t>1.4355e-20</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1271</v>
+        <v>1265</v>
       </c>
       <c r="H2" t="n">
-        <v>0.22934</v>
+        <v>0.24966</v>
       </c>
     </row>
     <row r="3">
@@ -515,34 +515,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>peak_mean_height</t>
+          <t>p10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.2430e-01</t>
+          <t>2.4813e-01</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.8736e-16</t>
+          <t>3.3413e-19</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2.1278e-01</t>
+          <t>2.5108e-01</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.7688e-14</t>
+          <t>1.2225e-19</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1271</v>
+        <v>1265</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2243</v>
+        <v>0.24813</v>
       </c>
     </row>
     <row r="4">
@@ -551,34 +551,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AUC</t>
+          <t>min</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.9897e-01</t>
+          <t>2.4697e-01</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.9583e-16</t>
+          <t>4.9386e-19</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.9693e-01</t>
+          <t>2.3674e-01</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>5.9777e-16</t>
+          <t>1.4235e-17</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H4" t="n">
-        <v>0.19897</v>
+        <v>0.24697</v>
       </c>
     </row>
     <row r="5">
@@ -587,34 +587,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>p25</t>
+          <t>p5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.9848e-01</t>
+          <t>2.4139e-01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.5089e-16</t>
+          <t>3.1449e-18</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.9172e-01</t>
+          <t>2.3510e-01</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3.5108e-15</t>
+          <t>2.4050e-17</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H5" t="n">
-        <v>0.19848</v>
+        <v>0.24139</v>
       </c>
     </row>
     <row r="6">
@@ -623,34 +623,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AUC_normalized</t>
+          <t>median</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.9630e-01</t>
+          <t>2.3935e-01</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.4266e-16</t>
+          <t>6.1197e-18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.8054e-01</t>
+          <t>2.3958e-01</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.3186e-13</t>
+          <t>5.6872e-18</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1963</v>
+        <v>0.23935</v>
       </c>
     </row>
     <row r="7">
@@ -659,34 +659,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>signal_energy</t>
+          <t>AUC_normalized</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.9613e-01</t>
+          <t>2.3926e-01</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.8806e-16</t>
+          <t>6.2968e-18</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.9437e-01</t>
+          <t>2.3085e-01</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.4357e-15</t>
+          <t>9.1731e-17</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H7" t="n">
-        <v>0.19613</v>
+        <v>0.23926</v>
       </c>
     </row>
     <row r="8">
@@ -700,29 +700,29 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.9597e-01</t>
+          <t>2.3910e-01</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3222e-16</t>
+          <t>6.6482e-18</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.8002e-01</t>
+          <t>2.3072e-01</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.5492e-13</t>
+          <t>9.5549e-17</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H8" t="n">
-        <v>0.19597</v>
+        <v>0.2391</v>
       </c>
     </row>
     <row r="9">
@@ -731,34 +731,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>median</t>
+          <t>peak_max_height</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.9530e-01</t>
+          <t>2.3284e-01</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.0465e-15</t>
+          <t>4.9057e-17</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.8377e-01</t>
+          <t>2.1505e-01</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>4.7256e-14</t>
+          <t>1.0596e-14</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1953</v>
+        <v>0.23284</v>
       </c>
     </row>
     <row r="10">
@@ -767,34 +767,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>peak_mean_height</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.9238e-01</t>
+          <t>2.2811e-01</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.8097e-15</t>
+          <t>2.1466e-16</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.7272e-01</t>
+          <t>2.1821e-01</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.4553e-12</t>
+          <t>4.2205e-15</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H10" t="n">
-        <v>0.19238</v>
+        <v>0.22811</v>
       </c>
     </row>
     <row r="11">
@@ -803,34 +803,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>wavelet_cA_energy</t>
+          <t>max</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.9091e-01</t>
+          <t>2.2113e-01</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4.5955e-15</t>
+          <t>1.7811e-15</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.8956e-01</t>
+          <t>2.0606e-01</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>7.1840e-15</t>
+          <t>1.3509e-13</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H11" t="n">
-        <v>0.19091</v>
+        <v>0.22113</v>
       </c>
     </row>
     <row r="12">
@@ -839,34 +839,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>p95</t>
+          <t>p75</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.8935e-01</t>
+          <t>2.1937e-01</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7.7055e-15</t>
+          <t>3.0002e-15</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.7109e-01</t>
+          <t>2.0271e-01</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2.3646e-12</t>
+          <t>3.3778e-13</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H12" t="n">
-        <v>0.18935</v>
+        <v>0.21937</v>
       </c>
     </row>
     <row r="13">
@@ -875,34 +875,34 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>p10</t>
+          <t>p95</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.8607e-01</t>
+          <t>2.1868e-01</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.2530e-14</t>
+          <t>3.6821e-15</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.8103e-01</t>
+          <t>2.0424e-01</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.1278e-13</t>
+          <t>2.2287e-13</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H13" t="n">
-        <v>0.18607</v>
+        <v>0.21868</v>
       </c>
     </row>
     <row r="14">
@@ -916,29 +916,29 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.8578e-01</t>
+          <t>2.1696e-01</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.4764e-14</t>
+          <t>6.0931e-15</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.6738e-01</t>
+          <t>2.0137e-01</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>7.0530e-12</t>
+          <t>4.8537e-13</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H14" t="n">
-        <v>0.18578</v>
+        <v>0.21696</v>
       </c>
     </row>
     <row r="15">
@@ -947,34 +947,34 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>p75</t>
+          <t>AUC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.8547e-01</t>
+          <t>2.0892e-01</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.7379e-14</t>
+          <t>6.0885e-14</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.6551e-01</t>
+          <t>2.2298e-01</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.2085e-11</t>
+          <t>1.0227e-15</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H15" t="n">
-        <v>0.18547</v>
+        <v>0.20892</v>
       </c>
     </row>
     <row r="16">
@@ -983,34 +983,34 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>signal_energy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.7566e-01</t>
+          <t>2.0849e-01</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5.9735e-13</t>
+          <t>6.8648e-14</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.6743e-01</t>
+          <t>2.2891e-01</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>6.9384e-12</t>
+          <t>1.6781e-16</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H16" t="n">
-        <v>0.17566</v>
+        <v>0.20849</v>
       </c>
     </row>
     <row r="17">
@@ -1019,34 +1019,34 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>wavelet_cA_energy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.7338e-01</t>
+          <t>2.0379e-01</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.1920e-12</t>
+          <t>2.5190e-13</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.6589e-01</t>
+          <t>2.2539e-01</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.0845e-11</t>
+          <t>4.9412e-16</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H17" t="n">
-        <v>0.17338</v>
+        <v>0.20379</v>
       </c>
     </row>
     <row r="18">
@@ -1060,29 +1060,29 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.1524e-01</t>
+          <t>1.4607e-01</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2.5624e-06</t>
+          <t>1.8065e-07</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.2011e-01</t>
+          <t>2.0907e-01</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>9.4210e-07</t>
+          <t>5.8383e-14</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H18" t="n">
-        <v>0.11524</v>
+        <v>0.14607</v>
       </c>
     </row>
     <row r="19">
@@ -1096,29 +1096,29 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.0883e-01</t>
+          <t>1.4015e-01</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.9933e-06</t>
+          <t>5.6021e-07</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>9.9056e-02</t>
+          <t>1.7521e-01</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>5.3660e-05</t>
+          <t>3.5139e-10</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H19" t="n">
-        <v>0.10883</v>
+        <v>0.14015</v>
       </c>
     </row>
     <row r="20">
@@ -1127,34 +1127,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>slope_min</t>
+          <t>CV</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-9.1888e-02</t>
+          <t>-1.2574e-01</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.8002e-04</t>
+          <t>7.2745e-06</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>-1.0300e-01</t>
+          <t>-1.3374e-01</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2.6624e-05</t>
+          <t>1.8099e-06</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H20" t="n">
-        <v>0.091888</v>
+        <v>0.12574</v>
       </c>
     </row>
     <row r="21">
@@ -1163,34 +1163,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>p90_p10_ratio</t>
+          <t>slope_min</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-8.9932e-02</t>
+          <t>-1.2290e-01</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.4687e-04</t>
+          <t>1.1673e-05</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>-7.9211e-02</t>
+          <t>-1.8374e-01</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.2509e-03</t>
+          <t>4.5564e-11</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H21" t="n">
-        <v>0.089932</v>
+        <v>0.1229</v>
       </c>
     </row>
     <row r="22">
@@ -1199,34 +1199,34 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>slope_std</t>
+          <t>p90_p10_ratio</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>8.8665e-02</t>
+          <t>-1.1847e-01</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3.0195e-04</t>
+          <t>2.3947e-05</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.1539e-01</t>
+          <t>-1.2591e-01</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2.4842e-06</t>
+          <t>7.0652e-06</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H22" t="n">
-        <v>0.08866499999999999</v>
+        <v>0.11847</v>
       </c>
     </row>
     <row r="23">
@@ -1235,34 +1235,34 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CV</t>
+          <t>wavelet_cD2_std</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-8.6095e-02</t>
+          <t>1.1641e-01</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4.5066e-04</t>
+          <t>3.3221e-05</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>-8.4546e-02</t>
+          <t>1.7002e-01</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>5.7078e-04</t>
+          <t>1.1624e-09</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H23" t="n">
-        <v>0.086095</v>
+        <v>0.11641</v>
       </c>
     </row>
     <row r="24">
@@ -1271,34 +1271,34 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>wavelet_cD2_std</t>
+          <t>slope_std</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>8.2439e-02</t>
+          <t>1.1251e-01</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7.8235e-04</t>
+          <t>6.0603e-05</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>9.2837e-02</t>
+          <t>2.0403e-01</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.5409e-04</t>
+          <t>2.3587e-13</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H24" t="n">
-        <v>0.082439</v>
+        <v>0.11251</v>
       </c>
     </row>
     <row r="25">
@@ -1307,34 +1307,34 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>slope_abs_mean</t>
+          <t>range</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>8.1042e-02</t>
+          <t>1.0665e-01</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>9.6052e-04</t>
+          <t>1.4459e-04</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.1361e-01</t>
+          <t>8.8321e-02</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>3.5471e-06</t>
+          <t>1.6647e-03</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H25" t="n">
-        <v>0.081042</v>
+        <v>0.10665</v>
       </c>
     </row>
     <row r="26">
@@ -1343,34 +1343,34 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>signal_length</t>
+          <t>slope_abs_mean</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>7.8057e-02</t>
+          <t>1.0129e-01</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1.4734e-03</t>
+          <t>3.0805e-04</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2.2585e-01</t>
+          <t>1.9805e-01</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1.3160e-20</t>
+          <t>1.1807e-12</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H26" t="n">
-        <v>0.078057</v>
+        <v>0.10129</v>
       </c>
     </row>
     <row r="27">
@@ -1379,34 +1379,34 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>wavelet_cD1_std</t>
+          <t>wavelet_cD3_std</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>7.5254e-02</t>
+          <t>9.8708e-02</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2.1743e-03</t>
+          <t>4.3836e-04</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>8.9412e-02</t>
+          <t>1.1474e-01</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2.6823e-04</t>
+          <t>4.3044e-05</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H27" t="n">
-        <v>0.075254</v>
+        <v>0.098708</v>
       </c>
     </row>
     <row r="28">
@@ -1415,34 +1415,34 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>spectral_energy</t>
+          <t>wavelet_cD1_std</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>7.4582e-02</t>
+          <t>9.1249e-02</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2.3823e-03</t>
+          <t>1.1580e-03</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2.8181e-02</t>
+          <t>1.5812e-01</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2.5159e-01</t>
+          <t>1.5685e-08</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H28" t="n">
-        <v>0.074582</v>
+        <v>0.091249</v>
       </c>
     </row>
     <row r="29">
@@ -1451,34 +1451,34 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>band1_energy</t>
+          <t>fft_mag_mean</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>7.1458e-02</t>
+          <t>8.5660e-02</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3.6105e-03</t>
+          <t>2.2942e-03</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2.8144e-02</t>
+          <t>5.5316e-02</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2.5222e-01</t>
+          <t>4.9186e-02</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H29" t="n">
-        <v>0.07145799999999999</v>
+        <v>0.08566</v>
       </c>
     </row>
     <row r="30">
@@ -1487,34 +1487,34 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>range</t>
+          <t>spectral_energy</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>6.9102e-02</t>
+          <t>8.4760e-02</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4.8912e-03</t>
+          <t>2.5520e-03</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>4.4936e-02</t>
+          <t>5.5455e-02</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>6.7444e-02</t>
+          <t>4.8619e-02</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H30" t="n">
-        <v>0.069102</v>
+        <v>0.08476</v>
       </c>
     </row>
     <row r="31">
@@ -1528,29 +1528,29 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>6.5488e-02</t>
+          <t>8.4606e-02</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>7.6622e-03</t>
+          <t>2.5988e-03</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>7.6292e-02</t>
+          <t>1.3194e-01</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1.8851e-03</t>
+          <t>2.4917e-06</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H31" t="n">
-        <v>0.065488</v>
+        <v>0.084606</v>
       </c>
     </row>
     <row r="32">
@@ -1559,34 +1559,34 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>wavelet_cD3_std</t>
+          <t>band1_energy</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>6.4973e-02</t>
+          <t>8.0972e-02</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>8.1547e-03</t>
+          <t>3.9539e-03</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>5.6569e-02</t>
+          <t>5.5059e-02</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2.1288e-02</t>
+          <t>5.0252e-02</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H32" t="n">
-        <v>0.064973</v>
+        <v>0.080972</v>
       </c>
     </row>
     <row r="33">
@@ -1595,34 +1595,34 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>peak_main_pos</t>
+          <t>valley_count</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>6.4461e-02</t>
+          <t>7.9113e-02</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2.1548e-02</t>
+          <t>4.8712e-03</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>7.1622e-02</t>
+          <t>1.0346e-01</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1.0644e-02</t>
+          <t>2.2792e-04</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1271</v>
+        <v>1265</v>
       </c>
       <c r="H33" t="n">
-        <v>0.064461</v>
+        <v>0.079113</v>
       </c>
     </row>
     <row r="34">
@@ -1631,34 +1631,34 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>band2_energy</t>
+          <t>fft_mag_std</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>6.3911e-02</t>
+          <t>7.8868e-02</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>9.2602e-03</t>
+          <t>5.0055e-03</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.6772e-02</t>
+          <t>4.3920e-02</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>4.9509e-01</t>
+          <t>1.1846e-01</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H34" t="n">
-        <v>0.063911</v>
+        <v>0.07886799999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1667,34 +1667,34 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>peak_last_pos</t>
+          <t>peak_count</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>6.1621e-02</t>
+          <t>7.4581e-02</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2.8035e-02</t>
+          <t>7.9619e-03</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2.7827e-02</t>
+          <t>8.4104e-02</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>3.2154e-01</t>
+          <t>2.7566e-03</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1271</v>
+        <v>1265</v>
       </c>
       <c r="H35" t="n">
-        <v>0.061621</v>
+        <v>0.07458099999999999</v>
       </c>
     </row>
     <row r="36">
@@ -1703,34 +1703,34 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>peak_max_width</t>
+          <t>kurtosis</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>6.1356e-02</t>
+          <t>7.1051e-02</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2.8720e-02</t>
+          <t>1.1480e-02</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.0038e-01</t>
+          <t>1.8797e-01</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>3.3820e-04</t>
+          <t>1.5952e-11</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1271</v>
+        <v>1265</v>
       </c>
       <c r="H36" t="n">
-        <v>0.061356</v>
+        <v>0.071051</v>
       </c>
     </row>
     <row r="37">
@@ -1739,34 +1739,34 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>valley_count</t>
+          <t>band2_energy</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>6.0903e-02</t>
+          <t>7.0927e-02</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>1.3155e-02</t>
+          <t>1.1625e-02</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>5.8968e-02</t>
+          <t>4.3298e-02</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1.6367e-02</t>
+          <t>1.2376e-01</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H37" t="n">
-        <v>0.060903</v>
+        <v>0.070927</v>
       </c>
     </row>
     <row r="38">
@@ -1775,34 +1775,34 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>fft_mag_mean</t>
+          <t>wavelet_cA_std</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>5.6430e-02</t>
+          <t>6.7671e-02</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2.1609e-02</t>
+          <t>1.6075e-02</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2.4496e-02</t>
+          <t>3.7192e-02</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>3.1899e-01</t>
+          <t>1.8618e-01</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H38" t="n">
-        <v>0.05643</v>
+        <v>0.067671</v>
       </c>
     </row>
     <row r="39">
@@ -1811,34 +1811,34 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>peak_count</t>
+          <t>peak_main_pos</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>5.3181e-02</t>
+          <t>6.7117e-02</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>3.0411e-02</t>
+          <t>1.6964e-02</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>4.4401e-02</t>
+          <t>7.5958e-02</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>7.0775e-02</t>
+          <t>6.8753e-03</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H39" t="n">
-        <v>0.053181</v>
+        <v>0.067117</v>
       </c>
     </row>
     <row r="40">
@@ -1847,34 +1847,34 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>fft_mag_std</t>
+          <t>peak_max_width</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>5.0735e-02</t>
+          <t>6.5346e-02</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3.8923e-02</t>
+          <t>2.0107e-02</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2.1592e-02</t>
+          <t>1.0568e-01</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>3.7975e-01</t>
+          <t>1.6615e-04</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H40" t="n">
-        <v>0.050735</v>
+        <v>0.065346</v>
       </c>
     </row>
     <row r="41">
@@ -1883,34 +1883,34 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>band3_energy</t>
+          <t>RMSE</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>4.9100e-02</t>
+          <t>6.4257e-02</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>4.5675e-02</t>
+          <t>2.2283e-02</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.1668e-02</t>
+          <t>3.5192e-02</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>6.3505e-01</t>
+          <t>2.1100e-01</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H41" t="n">
-        <v>0.0491</v>
+        <v>0.06425699999999999</v>
       </c>
     </row>
     <row r="42">
@@ -1919,34 +1919,34 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>peak_std_height</t>
+          <t>std</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>4.1211e-02</t>
+          <t>6.4166e-02</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.4199e-01</t>
+          <t>2.2473e-02</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.6695e-02</t>
+          <t>3.5177e-02</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>5.5207e-01</t>
+          <t>2.1119e-01</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1271</v>
+        <v>1265</v>
       </c>
       <c r="H42" t="n">
-        <v>0.041211</v>
+        <v>0.064166</v>
       </c>
     </row>
     <row r="43">
@@ -1955,34 +1955,34 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>wavelet_cD2_energy</t>
+          <t>peak_last_pos</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>4.0978e-02</t>
+          <t>5.9961e-02</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>9.5415e-02</t>
+          <t>3.2971e-02</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.1140e-01</t>
+          <t>2.4785e-02</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>5.4813e-06</t>
+          <t>3.7844e-01</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H43" t="n">
-        <v>0.040978</v>
+        <v>0.059961</v>
       </c>
     </row>
     <row r="44">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>wavelet_cA_std</t>
+          <t>signal_length</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>4.0094e-02</t>
+          <t>5.8675e-02</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1.0279e-01</t>
+          <t>3.6924e-02</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2.1872e-02</t>
+          <t>1.9434e-01</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>3.7360e-01</t>
+          <t>3.1294e-12</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H44" t="n">
-        <v>0.040094</v>
+        <v>0.058675</v>
       </c>
     </row>
     <row r="45">
@@ -2027,34 +2027,34 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>band4_energy</t>
+          <t>band3_energy</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>3.8786e-02</t>
+          <t>5.5413e-02</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1.1451e-01</t>
+          <t>4.8789e-02</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>6.9963e-03</t>
+          <t>3.2181e-02</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>7.7597e-01</t>
+          <t>2.5273e-01</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H45" t="n">
-        <v>0.038786</v>
+        <v>0.055413</v>
       </c>
     </row>
     <row r="46">
@@ -2063,34 +2063,34 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>slope_mean</t>
+          <t>skewness</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>3.6988e-02</t>
+          <t>-5.0928e-02</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.3232e-01</t>
+          <t>7.0180e-02</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>6.2395e-02</t>
+          <t>-6.5750e-02</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1.1071e-02</t>
+          <t>1.9349e-02</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H46" t="n">
-        <v>0.036988</v>
+        <v>0.050928</v>
       </c>
     </row>
     <row r="47">
@@ -2099,34 +2099,34 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>RMSE</t>
+          <t>fft_mag_max</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>3.6842e-02</t>
+          <t>5.0362e-02</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>1.3385e-01</t>
+          <t>7.3360e-02</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.4241e-02</t>
+          <t>1.6125e-02</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>5.6239e-01</t>
+          <t>5.6665e-01</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H47" t="n">
-        <v>0.036842</v>
+        <v>0.050362</v>
       </c>
     </row>
     <row r="48">
@@ -2135,34 +2135,34 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>std</t>
+          <t>wavelet_cD2_energy</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>3.6769e-02</t>
+          <t>4.8007e-02</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1.3463e-01</t>
+          <t>8.7865e-02</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.4241e-02</t>
+          <t>1.9256e-01</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>5.6241e-01</t>
+          <t>4.9583e-12</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H48" t="n">
-        <v>0.036769</v>
+        <v>0.048007</v>
       </c>
     </row>
     <row r="49">
@@ -2171,34 +2171,34 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>wavelet_cD1_energy</t>
+          <t>first_high_pos</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>3.3931e-02</t>
+          <t>4.6881e-02</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1.6741e-01</t>
+          <t>9.5578e-02</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.0988e-01</t>
+          <t>2.3622e-02</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>7.3631e-06</t>
+          <t>4.0122e-01</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H49" t="n">
-        <v>0.033931</v>
+        <v>0.046881</v>
       </c>
     </row>
     <row r="50">
@@ -2207,34 +2207,34 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>skewness</t>
+          <t>band4_energy</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>-3.3580e-02</t>
+          <t>4.4523e-02</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2.2685e-01</t>
+          <t>1.1348e-01</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>-6.1424e-02</t>
+          <t>2.3737e-02</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2.6962e-02</t>
+          <t>3.9893e-01</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1297</v>
+        <v>1265</v>
       </c>
       <c r="H50" t="n">
-        <v>0.03358</v>
+        <v>0.044523</v>
       </c>
     </row>
     <row r="51">
@@ -2243,34 +2243,34 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>wavelet_energy_ratio_D1</t>
+          <t>dominant_freq</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>3.3564e-02</t>
+          <t>4.4317e-02</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1.7205e-01</t>
+          <t>1.1516e-01</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>7.3329e-03</t>
+          <t>-6.2843e-02</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>7.6549e-01</t>
+          <t>2.5409e-02</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H51" t="n">
-        <v>0.033564</v>
+        <v>0.044317</v>
       </c>
     </row>
     <row r="52">
@@ -2279,34 +2279,34 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>dominant_freq</t>
+          <t>peak_std_height</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>3.3547e-02</t>
+          <t>4.2509e-02</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.7228e-01</t>
+          <t>1.3077e-01</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>-7.4194e-02</t>
+          <t>1.3452e-02</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2.5108e-03</t>
+          <t>6.3266e-01</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H52" t="n">
-        <v>0.033547</v>
+        <v>0.042509</v>
       </c>
     </row>
     <row r="53">
@@ -2315,34 +2315,34 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>first_high_pos</t>
+          <t>spectral_centroid</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>3.3431e-02</t>
+          <t>4.2046e-02</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.7377e-01</t>
+          <t>1.3501e-01</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2.2223e-03</t>
+          <t>6.3285e-02</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>9.2798e-01</t>
+          <t>2.4393e-02</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H53" t="n">
-        <v>0.033431</v>
+        <v>0.042046</v>
       </c>
     </row>
     <row r="54">
@@ -2351,34 +2351,34 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>fft_mag_max</t>
+          <t>mean_abs_deviation</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>3.1977e-02</t>
+          <t>4.0496e-02</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1.9326e-01</t>
+          <t>1.5002e-01</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>6.6596e-03</t>
+          <t>1.1382e-02</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>7.8648e-01</t>
+          <t>6.8589e-01</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H54" t="n">
-        <v>0.031977</v>
+        <v>0.040496</v>
       </c>
     </row>
     <row r="55">
@@ -2387,34 +2387,34 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>band3_energy_ratio</t>
+          <t>wavelet_cD1_energy</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2.8452e-02</t>
+          <t>3.9561e-02</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2.5167e-01</t>
+          <t>1.5966e-01</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>-1.1725e-04</t>
+          <t>1.8230e-01</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>9.9623e-01</t>
+          <t>6.4734e-11</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>1625</v>
+        <v>1265</v>
       </c>
       <c r="H55" t="n">
-        <v>0.028452</v>
+        <v>0.039561</v>
       </c>
     </row>
     <row r="56">
@@ -2423,34 +2423,34 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>band4_energy_ratio</t>
+          <t>wavelet_energy_ratio_D1</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2.6343e-02</t>
+          <t>3.9153e-02</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2.8857e-01</t>
+          <t>1.6401e-01</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>-6.3266e-03</t>
+          <t>1.4208e-02</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>7.9885e-01</t>
+          <t>6.1366e-01</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1625</v>
+        <v>1265</v>
       </c>
       <c r="H56" t="n">
-        <v>0.026343</v>
+        <v>0.039153</v>
       </c>
     </row>
     <row r="57">
@@ -2459,34 +2459,34 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>spectral_centroid</t>
+          <t>spectral_rolloff</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2.3861e-02</t>
+          <t>3.7599e-02</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>3.3642e-01</t>
+          <t>1.8141e-01</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>3.7748e-02</t>
+          <t>5.9002e-02</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1.2825e-01</t>
+          <t>3.5882e-02</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>1625</v>
+        <v>1265</v>
       </c>
       <c r="H57" t="n">
-        <v>0.023861</v>
+        <v>0.037599</v>
       </c>
     </row>
     <row r="58">
@@ -2495,34 +2495,34 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>peak_first_pos</t>
+          <t>slope_mean</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>1.9652e-02</t>
+          <t>3.3539e-02</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>4.8394e-01</t>
+          <t>2.3325e-01</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>-1.1855e-03</t>
+          <t>6.5961e-02</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>9.6632e-01</t>
+          <t>1.8962e-02</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>1271</v>
+        <v>1265</v>
       </c>
       <c r="H58" t="n">
-        <v>0.019652</v>
+        <v>0.033539</v>
       </c>
     </row>
     <row r="59">
@@ -2531,34 +2531,34 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>mean_abs_deviation</t>
+          <t>peak_first_pos</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1.8461e-02</t>
+          <t>2.4679e-02</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>4.5267e-01</t>
+          <t>3.8048e-01</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2.4622e-04</t>
+          <t>4.7882e-03</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>9.9201e-01</t>
+          <t>8.6490e-01</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H59" t="n">
-        <v>0.018461</v>
+        <v>0.024679</v>
       </c>
     </row>
     <row r="60">
@@ -2567,34 +2567,34 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>band2_energy_ratio</t>
+          <t>band4_energy_ratio</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>-1.6064e-02</t>
+          <t>2.2996e-02</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>5.1757e-01</t>
+          <t>4.1382e-01</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2.2602e-03</t>
+          <t>-1.2172e-02</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>9.2746e-01</t>
+          <t>6.6538e-01</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>1625</v>
+        <v>1265</v>
       </c>
       <c r="H60" t="n">
-        <v>0.016064</v>
+        <v>0.022996</v>
       </c>
     </row>
     <row r="61">
@@ -2603,34 +2603,34 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>spectral_rolloff</t>
+          <t>band2_energy_ratio</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>1.5629e-02</t>
+          <t>-1.9266e-02</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>5.2897e-01</t>
+          <t>4.9358e-01</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>3.5184e-02</t>
+          <t>1.1576e-02</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1.5630e-01</t>
+          <t>6.8083e-01</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>1625</v>
+        <v>1265</v>
       </c>
       <c r="H61" t="n">
-        <v>0.015629</v>
+        <v>0.019266</v>
       </c>
     </row>
     <row r="62">
@@ -2639,34 +2639,34 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>peak_mean_width</t>
+          <t>band1_energy_ratio</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>-1.1356e-02</t>
+          <t>-1.8423e-02</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>6.8588e-01</t>
+          <t>5.1268e-01</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.3747e-02</t>
+          <t>-7.2997e-03</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>6.2440e-01</t>
+          <t>7.9535e-01</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>1271</v>
+        <v>1265</v>
       </c>
       <c r="H62" t="n">
-        <v>0.011356</v>
+        <v>0.018423</v>
       </c>
     </row>
     <row r="63">
@@ -2675,34 +2675,34 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>band1_energy_ratio</t>
+          <t>IQR</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>-1.1137e-02</t>
+          <t>1.2940e-02</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>6.5372e-01</t>
+          <t>6.4565e-01</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>-3.6780e-03</t>
+          <t>-2.2099e-02</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>8.8222e-01</t>
+          <t>4.3226e-01</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>1625</v>
+        <v>1265</v>
       </c>
       <c r="H63" t="n">
-        <v>0.011137</v>
+        <v>0.01294</v>
       </c>
     </row>
     <row r="64">
@@ -2711,34 +2711,34 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>spectral_spread</t>
+          <t>band3_energy_ratio</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>5.6195e-03</t>
+          <t>1.0505e-02</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>8.2092e-01</t>
+          <t>7.0895e-01</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>1.5870e-03</t>
+          <t>1.2774e-03</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>9.4903e-01</t>
+          <t>9.6380e-01</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>1625</v>
+        <v>1265</v>
       </c>
       <c r="H64" t="n">
-        <v>0.0056195</v>
+        <v>0.010505</v>
       </c>
     </row>
     <row r="65">
@@ -2747,34 +2747,34 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>IQR</t>
+          <t>spectral_spread</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>-4.6620e-03</t>
+          <t>7.8983e-03</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>8.4960e-01</t>
+          <t>7.7898e-01</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>-2.3008e-02</t>
+          <t>2.4393e-03</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>3.4929e-01</t>
+          <t>9.3093e-01</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H65" t="n">
-        <v>0.004662</v>
+        <v>0.0078983</v>
       </c>
     </row>
     <row r="66">
@@ -2783,34 +2783,34 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>kurtosis</t>
+          <t>peak_mean_width</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>-2.5330e-03</t>
+          <t>-5.6066e-03</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>9.2738e-01</t>
+          <t>8.4210e-01</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>1.8374e-01</t>
+          <t>1.8433e-02</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2.5960e-11</t>
+          <t>5.1247e-01</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>1297</v>
+        <v>1265</v>
       </c>
       <c r="H66" t="n">
-        <v>0.002533</v>
+        <v>0.0056066</v>
       </c>
     </row>
   </sheetData>
@@ -2875,34 +2875,34 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>peak_max_height</t>
+          <t>p25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2.2934e-01</t>
+          <t>2.4966e-01</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.2455e-16</t>
+          <t>1.9851e-19</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2.0972e-01</t>
+          <t>2.5726e-01</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>4.2336e-14</t>
+          <t>1.4355e-20</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1271</v>
+        <v>1265</v>
       </c>
       <c r="H2" t="n">
-        <v>0.22934</v>
+        <v>0.24966</v>
       </c>
     </row>
     <row r="3">
@@ -2911,34 +2911,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>peak_mean_height</t>
+          <t>p10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2.2430e-01</t>
+          <t>2.4813e-01</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.8736e-16</t>
+          <t>3.3413e-19</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2.1278e-01</t>
+          <t>2.5108e-01</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.7688e-14</t>
+          <t>1.2225e-19</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1271</v>
+        <v>1265</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2243</v>
+        <v>0.24813</v>
       </c>
     </row>
     <row r="4">
@@ -2947,34 +2947,34 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AUC</t>
+          <t>min</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.9897e-01</t>
+          <t>2.4697e-01</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.9583e-16</t>
+          <t>4.9386e-19</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.9693e-01</t>
+          <t>2.3674e-01</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>5.9777e-16</t>
+          <t>1.4235e-17</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H4" t="n">
-        <v>0.19897</v>
+        <v>0.24697</v>
       </c>
     </row>
     <row r="5">
@@ -2983,34 +2983,34 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>p25</t>
+          <t>p5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.9848e-01</t>
+          <t>2.4139e-01</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.5089e-16</t>
+          <t>3.1449e-18</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.9172e-01</t>
+          <t>2.3510e-01</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3.5108e-15</t>
+          <t>2.4050e-17</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H5" t="n">
-        <v>0.19848</v>
+        <v>0.24139</v>
       </c>
     </row>
     <row r="6">
@@ -3019,34 +3019,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AUC_normalized</t>
+          <t>median</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.9630e-01</t>
+          <t>2.3935e-01</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.4266e-16</t>
+          <t>6.1197e-18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.8054e-01</t>
+          <t>2.3958e-01</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.3186e-13</t>
+          <t>5.6872e-18</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1963</v>
+        <v>0.23935</v>
       </c>
     </row>
     <row r="7">
@@ -3055,34 +3055,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>signal_energy</t>
+          <t>AUC_normalized</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.9613e-01</t>
+          <t>2.3926e-01</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.8806e-16</t>
+          <t>6.2968e-18</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.9437e-01</t>
+          <t>2.3085e-01</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.4357e-15</t>
+          <t>9.1731e-17</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H7" t="n">
-        <v>0.19613</v>
+        <v>0.23926</v>
       </c>
     </row>
     <row r="8">
@@ -3096,29 +3096,29 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.9597e-01</t>
+          <t>2.3910e-01</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.3222e-16</t>
+          <t>6.6482e-18</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.8002e-01</t>
+          <t>2.3072e-01</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.5492e-13</t>
+          <t>9.5549e-17</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H8" t="n">
-        <v>0.19597</v>
+        <v>0.2391</v>
       </c>
     </row>
     <row r="9">
@@ -3127,34 +3127,34 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>median</t>
+          <t>peak_max_height</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.9530e-01</t>
+          <t>2.3284e-01</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.0465e-15</t>
+          <t>4.9057e-17</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.8377e-01</t>
+          <t>2.1505e-01</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>4.7256e-14</t>
+          <t>1.0596e-14</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1953</v>
+        <v>0.23284</v>
       </c>
     </row>
     <row r="10">
@@ -3163,34 +3163,34 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>max</t>
+          <t>peak_mean_height</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.9238e-01</t>
+          <t>2.2811e-01</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.8097e-15</t>
+          <t>2.1466e-16</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.7272e-01</t>
+          <t>2.1821e-01</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.4553e-12</t>
+          <t>4.2205e-15</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H10" t="n">
-        <v>0.19238</v>
+        <v>0.22811</v>
       </c>
     </row>
     <row r="11">
@@ -3199,34 +3199,34 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>wavelet_cA_energy</t>
+          <t>max</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.9091e-01</t>
+          <t>2.2113e-01</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4.5955e-15</t>
+          <t>1.7811e-15</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.8956e-01</t>
+          <t>2.0606e-01</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>7.1840e-15</t>
+          <t>1.3509e-13</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H11" t="n">
-        <v>0.19091</v>
+        <v>0.22113</v>
       </c>
     </row>
     <row r="12">
@@ -3235,34 +3235,34 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>p95</t>
+          <t>p75</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.8935e-01</t>
+          <t>2.1937e-01</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>7.7055e-15</t>
+          <t>3.0002e-15</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.7109e-01</t>
+          <t>2.0271e-01</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2.3646e-12</t>
+          <t>3.3778e-13</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H12" t="n">
-        <v>0.18935</v>
+        <v>0.21937</v>
       </c>
     </row>
     <row r="13">
@@ -3271,34 +3271,34 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>p10</t>
+          <t>p95</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.8607e-01</t>
+          <t>2.1868e-01</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.2530e-14</t>
+          <t>3.6821e-15</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.8103e-01</t>
+          <t>2.0424e-01</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.1278e-13</t>
+          <t>2.2287e-13</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H13" t="n">
-        <v>0.18607</v>
+        <v>0.21868</v>
       </c>
     </row>
     <row r="14">
@@ -3312,29 +3312,29 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.8578e-01</t>
+          <t>2.1696e-01</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.4764e-14</t>
+          <t>6.0931e-15</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.6738e-01</t>
+          <t>2.0137e-01</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>7.0530e-12</t>
+          <t>4.8537e-13</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H14" t="n">
-        <v>0.18578</v>
+        <v>0.21696</v>
       </c>
     </row>
     <row r="15">
@@ -3343,34 +3343,34 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>p75</t>
+          <t>AUC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.8547e-01</t>
+          <t>2.0892e-01</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2.7379e-14</t>
+          <t>6.0885e-14</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.6551e-01</t>
+          <t>2.2298e-01</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1.2085e-11</t>
+          <t>1.0227e-15</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H15" t="n">
-        <v>0.18547</v>
+        <v>0.20892</v>
       </c>
     </row>
     <row r="16">
@@ -3379,34 +3379,34 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>signal_energy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.7566e-01</t>
+          <t>2.0849e-01</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>5.9735e-13</t>
+          <t>6.8648e-14</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.6743e-01</t>
+          <t>2.2891e-01</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>6.9384e-12</t>
+          <t>1.6781e-16</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H16" t="n">
-        <v>0.17566</v>
+        <v>0.20849</v>
       </c>
     </row>
     <row r="17">
@@ -3415,34 +3415,34 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>min</t>
+          <t>wavelet_cA_energy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.7338e-01</t>
+          <t>2.0379e-01</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.1920e-12</t>
+          <t>2.5190e-13</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.6589e-01</t>
+          <t>2.2539e-01</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.0845e-11</t>
+          <t>4.9412e-16</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H17" t="n">
-        <v>0.17338</v>
+        <v>0.20379</v>
       </c>
     </row>
     <row r="18">
@@ -3456,29 +3456,29 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.1524e-01</t>
+          <t>1.4607e-01</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2.5624e-06</t>
+          <t>1.8065e-07</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.2011e-01</t>
+          <t>2.0907e-01</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>9.4210e-07</t>
+          <t>5.8383e-14</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H18" t="n">
-        <v>0.11524</v>
+        <v>0.14607</v>
       </c>
     </row>
     <row r="19">
@@ -3492,29 +3492,29 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.0883e-01</t>
+          <t>1.4015e-01</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>8.9933e-06</t>
+          <t>5.6021e-07</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>9.9056e-02</t>
+          <t>1.7521e-01</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>5.3660e-05</t>
+          <t>3.5139e-10</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H19" t="n">
-        <v>0.10883</v>
+        <v>0.14015</v>
       </c>
     </row>
     <row r="20">
@@ -3523,34 +3523,34 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>slope_min</t>
+          <t>CV</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-9.1888e-02</t>
+          <t>-1.2574e-01</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.8002e-04</t>
+          <t>7.2745e-06</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>-1.0300e-01</t>
+          <t>-1.3374e-01</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2.6624e-05</t>
+          <t>1.8099e-06</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H20" t="n">
-        <v>0.091888</v>
+        <v>0.12574</v>
       </c>
     </row>
     <row r="21">
@@ -3559,34 +3559,34 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>p90_p10_ratio</t>
+          <t>slope_min</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-8.9932e-02</t>
+          <t>-1.2290e-01</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.4687e-04</t>
+          <t>1.1673e-05</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>-7.9211e-02</t>
+          <t>-1.8374e-01</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.2509e-03</t>
+          <t>4.5564e-11</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1657</v>
+        <v>1265</v>
       </c>
       <c r="H21" t="n">
-        <v>0.089932</v>
+        <v>0.1229</v>
       </c>
     </row>
   </sheetData>
@@ -3622,7 +3622,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>59.907</v>
+        <v>66.545</v>
       </c>
     </row>
     <row r="3">
@@ -3632,7 +3632,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55.027</v>
+        <v>61.697</v>
       </c>
     </row>
     <row r="4">
@@ -3642,7 +3642,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.53</v>
+        <v>2.605</v>
       </c>
     </row>
     <row r="5">
@@ -3652,7 +3652,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.351</v>
+        <v>1.355</v>
       </c>
     </row>
     <row r="6">
@@ -3662,7 +3662,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.107</v>
+        <v>1.109</v>
       </c>
     </row>
     <row r="7">
@@ -3682,7 +3682,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.053</v>
+        <v>1.049</v>
       </c>
     </row>
   </sheetData>
@@ -3763,34 +3763,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1143</v>
+        <v>637</v>
       </c>
       <c r="C2" t="n">
-        <v>149.03</v>
+        <v>147.92</v>
       </c>
       <c r="D2" t="n">
-        <v>26.62</v>
+        <v>26.92</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G2" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="H2" t="n">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I2" t="n">
         <v>279</v>
       </c>
       <c r="J2" t="n">
-        <v>117</v>
+        <v>116.6</v>
       </c>
       <c r="K2" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3">
@@ -3800,13 +3800,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1114</v>
+        <v>628</v>
       </c>
       <c r="C3" t="n">
-        <v>104.46</v>
+        <v>104.41</v>
       </c>
       <c r="D3" t="n">
-        <v>16.02</v>
+        <v>15.47</v>
       </c>
       <c r="E3" t="n">
         <v>29</v>
@@ -3815,16 +3815,16 @@
         <v>95</v>
       </c>
       <c r="G3" t="n">
-        <v>103</v>
+        <v>103.5</v>
       </c>
       <c r="H3" t="n">
         <v>114</v>
       </c>
       <c r="I3" t="n">
-        <v>191</v>
+        <v>158</v>
       </c>
       <c r="J3" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K3" t="n">
         <v>98</v>
